--- a/qoe-evidence-review/data/dev/tidewell_distribution/financials/monthly_pl.xlsx
+++ b/qoe-evidence-review/data/dev/tidewell_distribution/financials/monthly_pl.xlsx
@@ -1330,53 +1330,53 @@
           <t>5200 Vendor Rebates</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
+      <c r="B17" s="4" t="n">
+        <v>-165057.92</v>
+      </c>
       <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n">
-        <v>-169826.42</v>
-      </c>
-      <c r="E17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n">
+        <v>-166251.24</v>
+      </c>
       <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n">
-        <v>-150364.74</v>
-      </c>
-      <c r="H17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n">
+        <v>-162303.05</v>
+      </c>
       <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n">
-        <v>-154475.83</v>
-      </c>
-      <c r="K17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n">
+        <v>-171229.31</v>
+      </c>
       <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n">
-        <v>-191038.92</v>
-      </c>
-      <c r="N17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n">
+        <v>-164301.17</v>
+      </c>
       <c r="O17" s="4" t="n"/>
-      <c r="P17" s="4" t="n">
-        <v>-181928.2</v>
-      </c>
-      <c r="Q17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="4" t="n">
+        <v>-176360.34</v>
+      </c>
       <c r="R17" s="4" t="n"/>
-      <c r="S17" s="4" t="n">
-        <v>-171567.58</v>
-      </c>
-      <c r="T17" s="4" t="n"/>
+      <c r="S17" s="4" t="n"/>
+      <c r="T17" s="4" t="n">
+        <v>-155708.98</v>
+      </c>
       <c r="U17" s="4" t="n"/>
-      <c r="V17" s="4" t="n">
-        <v>-181581.01</v>
-      </c>
-      <c r="W17" s="4" t="n"/>
+      <c r="V17" s="4" t="n"/>
+      <c r="W17" s="4" t="n">
+        <v>-145875.74</v>
+      </c>
       <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="4" t="n">
-        <v>-185899.68</v>
-      </c>
-      <c r="Z17" s="4" t="n"/>
+      <c r="Y17" s="4" t="n"/>
+      <c r="Z17" s="4" t="n">
+        <v>-162499.86</v>
+      </c>
       <c r="AA17" s="4" t="n"/>
-      <c r="AB17" s="4" t="n">
-        <v>-174636.07</v>
-      </c>
+      <c r="AB17" s="4" t="n"/>
       <c r="AC17" s="4" t="n">
-        <v>-1561318.45</v>
+        <v>-1469587.61</v>
       </c>
     </row>
     <row r="18">
@@ -1568,88 +1568,88 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>4401602.91</v>
+        <v>4236544.99</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>4427036.35</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>4462498.01</v>
+        <v>4632324.43</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>4734160.03</v>
+        <v>4567908.79</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>4674598.81</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>4384675.55</v>
+        <v>4535040.29</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>4405482.99</v>
+        <v>4243179.94</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>4083923.77</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>3928706.37</v>
+        <v>4083182.2</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>4297033.69</v>
+        <v>4125804.38</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>4238155.84</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>4352544.92</v>
+        <v>4543583.84</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>4503682.6</v>
+        <v>4339381.43</v>
       </c>
       <c r="O20" s="5" t="n">
         <v>4776134.94</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>4795173.53</v>
+        <v>4977101.73</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>4928219.8</v>
+        <v>4751859.46</v>
       </c>
       <c r="R20" s="5" t="n">
         <v>4795996.46</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>4598912.26</v>
+        <v>4770479.84</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>4599423.12</v>
+        <v>4443714.14</v>
       </c>
       <c r="U20" s="5" t="n">
         <v>4457945.28</v>
       </c>
       <c r="V20" s="5" t="n">
-        <v>4161982.89</v>
+        <v>4343563.9</v>
       </c>
       <c r="W20" s="5" t="n">
-        <v>4490488.71</v>
+        <v>4344612.97</v>
       </c>
       <c r="X20" s="5" t="n">
         <v>4574324.96</v>
       </c>
       <c r="Y20" s="5" t="n">
-        <v>4460931.5</v>
+        <v>4646831.18</v>
       </c>
       <c r="Z20" s="5" t="n">
-        <v>4886843.15</v>
+        <v>4724343.29</v>
       </c>
       <c r="AA20" s="5" t="n">
         <v>4957531.1</v>
       </c>
       <c r="AB20" s="5" t="n">
-        <v>4991246.79</v>
+        <v>5165882.86</v>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>122369256.33</v>
+        <v>122460987.17</v>
       </c>
     </row>
     <row r="21">
@@ -1659,88 +1659,88 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>1565693.8</v>
+        <v>1730751.72</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1729707.12</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1948827.65</v>
+        <v>1779001.23</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1587696.53</v>
+        <v>1753947.77</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>1726765.36</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1767548.4</v>
+        <v>1617183.66</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1449163.62</v>
+        <v>1611466.67</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>1624110.03</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1560792.41</v>
+        <v>1406316.58</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1521095.5</v>
+        <v>1692324.81</v>
       </c>
       <c r="L21" s="4" t="n">
         <v>1528284.42</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1776089.96</v>
+        <v>1585051.04</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1778765.39</v>
+        <v>1943066.56</v>
       </c>
       <c r="O21" s="4" t="n">
         <v>1652002.29</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1888286.32</v>
+        <v>1706358.12</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1728291.29</v>
+        <v>1904651.63</v>
       </c>
       <c r="R21" s="4" t="n">
         <v>1915502.12</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1794910.34</v>
+        <v>1623342.76</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1597909.54</v>
+        <v>1753618.52</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>1523405.01</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1650526.45</v>
+        <v>1468945.44</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1660880.23</v>
+        <v>1806755.97</v>
       </c>
       <c r="X21" s="4" t="n">
         <v>1424325.81</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1939424.85</v>
+        <v>1753525.17</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1704086.62</v>
+        <v>1866586.48</v>
       </c>
       <c r="AA21" s="4" t="n">
         <v>1796497.75</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>2045902.52</v>
+        <v>1871266.45</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>45886491.33</v>
+        <v>45794760.49</v>
       </c>
     </row>
     <row r="22">
@@ -4425,88 +4425,88 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>517203.7</v>
+        <v>682261.62</v>
       </c>
       <c r="C53" s="4" t="n">
         <v>662179.02</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>891304.74</v>
+        <v>721478.3199999999</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>489300.1</v>
+        <v>655551.34</v>
       </c>
       <c r="F53" s="4" t="n">
         <v>655463.4300000001</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>691963.98</v>
+        <v>541599.24</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>385752.06</v>
+        <v>548055.11</v>
       </c>
       <c r="I53" s="4" t="n">
         <v>510978.06</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>492085.73</v>
+        <v>337609.9</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>422457.11</v>
+        <v>593686.42</v>
       </c>
       <c r="L53" s="4" t="n">
         <v>417857.2</v>
       </c>
       <c r="M53" s="4" t="n">
-        <v>688232.4300000001</v>
+        <v>497193.51</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>679563.66</v>
+        <v>843864.83</v>
       </c>
       <c r="O53" s="4" t="n">
         <v>553938.6899999999</v>
       </c>
       <c r="P53" s="4" t="n">
-        <v>775092.65</v>
+        <v>593164.45</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>548327.6</v>
+        <v>724687.9399999999</v>
       </c>
       <c r="R53" s="4" t="n">
         <v>743392.38</v>
       </c>
       <c r="S53" s="4" t="n">
-        <v>639398.75</v>
+        <v>467831.17</v>
       </c>
       <c r="T53" s="4" t="n">
-        <v>370102.27</v>
+        <v>525811.25</v>
       </c>
       <c r="U53" s="4" t="n">
         <v>331967.46</v>
       </c>
       <c r="V53" s="4" t="n">
-        <v>494462.86</v>
+        <v>312881.85</v>
       </c>
       <c r="W53" s="4" t="n">
-        <v>493452.55</v>
+        <v>639328.29</v>
       </c>
       <c r="X53" s="4" t="n">
         <v>221872.81</v>
       </c>
       <c r="Y53" s="4" t="n">
-        <v>557635.92</v>
+        <v>371736.24</v>
       </c>
       <c r="Z53" s="4" t="n">
-        <v>586348.77</v>
+        <v>748848.63</v>
       </c>
       <c r="AA53" s="4" t="n">
         <v>693166.4399999999</v>
       </c>
       <c r="AB53" s="4" t="n">
-        <v>928098.09</v>
+        <v>753462.02</v>
       </c>
       <c r="AC53" s="4" t="n">
-        <v>15441598.46</v>
+        <v>15349867.62</v>
       </c>
     </row>
     <row r="54">
@@ -5081,88 +5081,88 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>447121.78</v>
+        <v>612179.7</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>653046.46</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>821589.09</v>
+        <v>651762.67</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>481470.75</v>
+        <v>647721.99</v>
       </c>
       <c r="F63" s="5" t="n">
         <v>645080.22</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>620189.48</v>
+        <v>469824.74</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>375821.34</v>
+        <v>538124.39</v>
       </c>
       <c r="I63" s="5" t="n">
         <v>503205.68</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>422309.38</v>
+        <v>267833.55</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>415109.74</v>
+        <v>586339.05</v>
       </c>
       <c r="L63" s="5" t="n">
         <v>409498.23</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>679245.0699999999</v>
+        <v>488206.15</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>604416.38</v>
+        <v>768717.55</v>
       </c>
       <c r="O63" s="5" t="n">
         <v>546299.92</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>699606.04</v>
+        <v>517677.84</v>
       </c>
       <c r="Q63" s="5" t="n">
-        <v>539482.64</v>
+        <v>715842.98</v>
       </c>
       <c r="R63" s="5" t="n">
         <v>735551.63</v>
       </c>
       <c r="S63" s="5" t="n">
-        <v>563764.7</v>
+        <v>392197.12</v>
       </c>
       <c r="T63" s="5" t="n">
-        <v>361678.36</v>
+        <v>517387.34</v>
       </c>
       <c r="U63" s="5" t="n">
         <v>369249.85</v>
       </c>
       <c r="V63" s="5" t="n">
-        <v>420645.43</v>
+        <v>239064.42</v>
       </c>
       <c r="W63" s="5" t="n">
-        <v>441178.38</v>
+        <v>587054.12</v>
       </c>
       <c r="X63" s="5" t="n">
         <v>204310.9</v>
       </c>
       <c r="Y63" s="5" t="n">
-        <v>538959.54</v>
+        <v>353059.86</v>
       </c>
       <c r="Z63" s="5" t="n">
-        <v>497458.89</v>
+        <v>659958.75</v>
       </c>
       <c r="AA63" s="5" t="n">
         <v>674519.49</v>
       </c>
       <c r="AB63" s="5" t="n">
-        <v>839172.3100000001</v>
+        <v>664536.24</v>
       </c>
       <c r="AC63" s="5" t="n">
-        <v>14509981.68</v>
+        <v>14418250.84</v>
       </c>
     </row>
   </sheetData>
